--- a/backtest_runs/20260410_193731/by_symbol/NCPL/NCPL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NCPL/NCPL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3306.520000000014</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96693.47999999998</v>
@@ -633,7 +633,7 @@
         <v>-5128.479999999987</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>97334.54000000001</v>
@@ -679,7 +679,7 @@
         <v>-11032.98000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>86301.56</v>
@@ -817,7 +817,7 @@
         <v>-3458.349999999995</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>96524.78</v>
@@ -863,7 +863,7 @@
         <v>-2648.590000000001</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>93876.19</v>
@@ -909,7 +909,7 @@
         <v>-8839.880000000003</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>85036.31</v>
@@ -1047,7 +1047,7 @@
         <v>-2867.900000000005</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>87026.96999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-6528.690000000008</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>89591.20999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-50.61000000000192</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>89540.59999999999</v>
@@ -1277,7 +1277,7 @@
         <v>-7574.630000000004</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>81965.96999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-5938.240000000005</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>85221.87999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1180.899999999993</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>84040.98</v>
@@ -1553,7 +1553,7 @@
         <v>-708.5400000000029</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>86942.62</v>
